--- a/astro-site/public/dl/kit-gestion-personal/BONUS-01-briefing-cambio-turno.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/BONUS-01-briefing-cambio-turno.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Briefing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Briefing" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -102,7 +102,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -124,30 +124,76 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -507,15 +553,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -523,6 +570,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -558,9 +606,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -603,8 +649,25 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -613,15 +676,15 @@
   <sheetPr>
     <tabColor rgb="00F57F17"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="50"/>
-    <col customWidth="1" max="3" min="3" width="20"/>
-    <col customWidth="1" max="4" min="4" width="20"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -638,6 +701,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="6" t="inlineStr">
         <is>
@@ -660,6 +724,7 @@
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
@@ -719,6 +784,7 @@
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
@@ -778,6 +844,7 @@
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="n"/>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
@@ -837,6 +904,7 @@
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
@@ -896,6 +964,7 @@
       <c r="C37" s="10" t="n"/>
       <c r="D37" s="10" t="n"/>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
@@ -949,6 +1018,7 @@
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="10" t="n"/>
     </row>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
@@ -958,13 +1028,23 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
+      <c r="B47" s="12" t="n"/>
+      <c r="C47" s="12" t="n"/>
+      <c r="D47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
+      <c r="B48" s="12" t="n"/>
+      <c r="C48" s="12" t="n"/>
+      <c r="D48" s="13" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
-    </row>
+      <c r="B49" s="12" t="n"/>
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="13" t="n"/>
+    </row>
+    <row r="50"/>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
@@ -993,16 +1073,25 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A39:D39"/>
     <mergeCell ref="A47:D47"/>
     <mergeCell ref="A49:D49"/>
     <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A46:D46"/>
     <mergeCell ref="A7:D7"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/BONUS-01-briefing-cambio-turno.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/BONUS-01-briefing-cambio-turno.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Briefing" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Briefing" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -102,7 +102,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -124,76 +124,30 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E0E0E0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E0E0E0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E0E0E0"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00E0E0E0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E0E0E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00E0E0E0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E0E0E0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E0E0E0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="12">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="2" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="1" fillId="2" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -553,16 +507,15 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="B2:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
+    <col customWidth="1" max="1" min="1" width="3"/>
+    <col customWidth="1" max="2" min="2" width="80"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -570,7 +523,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -606,7 +558,9 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="B9" t="inlineStr"/>
+    </row>
     <row r="10">
       <c r="B10" s="2" t="inlineStr">
         <is>
@@ -649,25 +603,8 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
 
@@ -676,15 +613,15 @@
   <sheetPr>
     <tabColor rgb="00F57F17"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col customWidth="1" max="1" min="1" width="5"/>
+    <col customWidth="1" max="2" min="2" width="50"/>
+    <col customWidth="1" max="3" min="3" width="20"/>
+    <col customWidth="1" max="4" min="4" width="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -701,7 +638,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="6" t="inlineStr">
         <is>
@@ -724,7 +660,6 @@
       <c r="C5" s="7" t="n"/>
       <c r="D5" s="7" t="n"/>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
@@ -784,7 +719,6 @@
       <c r="C13" s="10" t="n"/>
       <c r="D13" s="10" t="n"/>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
@@ -844,7 +778,6 @@
       <c r="C21" s="10" t="n"/>
       <c r="D21" s="10" t="n"/>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
@@ -904,7 +837,6 @@
       <c r="C29" s="10" t="n"/>
       <c r="D29" s="10" t="n"/>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
@@ -964,7 +896,6 @@
       <c r="C37" s="10" t="n"/>
       <c r="D37" s="10" t="n"/>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
@@ -1018,7 +949,6 @@
       <c r="C44" s="10" t="n"/>
       <c r="D44" s="10" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
@@ -1028,23 +958,13 @@
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="13" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="13" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="13" t="n"/>
-    </row>
-    <row r="50"/>
+    </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
@@ -1073,25 +993,16 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="A47:D47"/>
     <mergeCell ref="A49:D49"/>
     <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A39:D39"/>
     <mergeCell ref="A48:D48"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A46:D46"/>
     <mergeCell ref="A7:D7"/>
   </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-gestion-personal/BONUS-01-briefing-cambio-turno.xlsx
+++ b/astro-site/public/dl/kit-gestion-personal/BONUS-01-briefing-cambio-turno.xlsx
@@ -10,15 +10,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Briefing" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Instrucciones'!$A$1:$B$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Briefing'!$A$1:$F$72</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="11">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,8 +87,25 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +122,21 @@
       <patternFill patternType="solid">
         <fgColor rgb="002D2D2D"/>
         <bgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEEEE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
       </patternFill>
     </fill>
   </fills>
@@ -172,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -189,10 +227,101 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -555,7 +684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -572,88 +701,130 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Cómo usar esta plantilla:</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>▸ El turno saliente completa este briefing ANTES de irse.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>▸ El turno entrante lo revisa y firma al llegar.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>▸ Imprime una copia diaria o usa en tablet.</t>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>▸ Imprime una copia diaria o úsalo en la tablet.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>▸ Archiva los briefings para trazabilidad.</t>
+      <c r="B8" s="15" t="inlineStr">
+        <is>
+          <t>▸ Archiva los briefings: son la trazabilidad del traspaso, y las temperaturas de abajo son además registro de autocontrol APPCC.</t>
         </is>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Secciones incluidas:</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>▸ Reservas pendientes y VIPs del siguiente turno.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>▸ Incidencias: averías, falta de stock, quejas.</t>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>▸ Incidencias: averías, falta de stock, quejas. La gravedad va con desplegable (Alta · Media · Baja): sin escala fija cada encargado escribe una cosa y el archivo deja de ser comparable.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>▸ Tareas pendientes que no se completaron.</t>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>▸ Tareas pendientes que no se completaron, con prioridad (Urgente · Alta · Normal).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>▸ Stock bajo que necesita pedido urgente.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>▸ Personal: ausencias y cambios de último momento.</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
+    <row r="16">
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <t>▸ CAJA — arqueo de verdad: fondo inicial, EFECTIVO CONTADO y VENTAS EN EFECTIVO según la lectura Z del TPV. El descuadre es contado − fondo − ventas, y el veredicto lo compara con la tolerancia que fijes arriba (5 € de fábrica). Sin la columna del TPV esto no sería un arqueo: sería la recaudación neta, un número que ya sabes y que un faltante de 80 € no cambia.</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>▸ Un FALTANTE sale en rojo y un SOBRANTE en ámbar: los dos son descuadres, pero un sobrante suele ser un cobro sin registrar y no un agujero de caja. Los dos se firman abajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>▸ TEMPERATURAS al cambio de turno: cámara, congelador, vitrina FRÍA, baño maría / mesa caliente y buffet o vitrina CALIENTE. Es el punto exacto en que el APPCC cambia de responsable. Cada equipo tiene MÍNIMO y máximo, no sólo un techo: una cámara a −5 °C te ha congelado el producto fresco y es no conformidad igual que una a 10 °C, y el mantenimiento en caliente sólo es conforme A PARTIR de 65 °C. La columna «Conforme» se pinta sola.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>▸ Observaciones generales: las tres líneas admiten texto largo (van con ajuste de línea y alto de fila, para que no se corten al imprimir).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Para editar una celda bloqueada: Revisar → Desproteger hoja (no tiene contraseña). Las celdas verdes ya son editables sin desproteger nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-gestion-personal · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -678,13 +849,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -720,9 +893,9 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
     </row>
     <row r="6"/>
     <row r="7">
@@ -755,36 +928,41 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n"/>
-      <c r="B9" s="10" t="n"/>
-      <c r="C9" s="10" t="n"/>
-      <c r="D9" s="10" t="n"/>
+      <c r="A9" s="17" t="n"/>
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="17" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
+      <c r="A10" s="17" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n"/>
-      <c r="B11" s="10" t="n"/>
-      <c r="C11" s="10" t="n"/>
-      <c r="D11" s="10" t="n"/>
+      <c r="A11" s="17" t="n"/>
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="17" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="10" t="n"/>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="10" t="n"/>
+      <c r="A12" s="17" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-    </row>
-    <row r="14"/>
+      <c r="A13" s="17" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+    </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
@@ -815,36 +993,41 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n"/>
-      <c r="B17" s="10" t="n"/>
-      <c r="C17" s="10" t="n"/>
-      <c r="D17" s="10" t="n"/>
+      <c r="A17" s="17" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="10" t="n"/>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="10" t="n"/>
+      <c r="A18" s="17" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
+      <c r="A19" s="17" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="10" t="n"/>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="10" t="n"/>
+      <c r="A20" s="17" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n"/>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-    </row>
-    <row r="22"/>
+      <c r="A21" s="17" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+    </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
@@ -875,36 +1058,40 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n"/>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="10" t="n"/>
+      <c r="A25" s="17" t="n"/>
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
+      <c r="A26" s="17" t="n"/>
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="10" t="n"/>
+      <c r="A27" s="17" t="n"/>
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
+      <c r="A28" s="17" t="n"/>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n"/>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="10" t="n"/>
-    </row>
-    <row r="30"/>
+      <c r="A29" s="17" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+    </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
@@ -935,36 +1122,41 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n"/>
-      <c r="B33" s="10" t="n"/>
-      <c r="C33" s="10" t="n"/>
-      <c r="D33" s="10" t="n"/>
+      <c r="A33" s="17" t="n"/>
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="10" t="n"/>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
+      <c r="A34" s="17" t="n"/>
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n"/>
-      <c r="B35" s="10" t="n"/>
-      <c r="C35" s="10" t="n"/>
-      <c r="D35" s="10" t="n"/>
+      <c r="A35" s="17" t="n"/>
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="10" t="n"/>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="10" t="n"/>
+      <c r="A36" s="17" t="n"/>
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n"/>
-      <c r="B37" s="10" t="n"/>
-      <c r="C37" s="10" t="n"/>
-      <c r="D37" s="10" t="n"/>
-    </row>
-    <row r="38"/>
+      <c r="A37" s="17" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="n"/>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+    </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
@@ -995,94 +1187,406 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="n"/>
-      <c r="B41" s="10" t="n"/>
-      <c r="C41" s="10" t="n"/>
-      <c r="D41" s="10" t="n"/>
+      <c r="A41" s="17" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n"/>
-      <c r="B42" s="10" t="n"/>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="10" t="n"/>
+      <c r="A42" s="17" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n"/>
-      <c r="B43" s="10" t="n"/>
-      <c r="C43" s="10" t="n"/>
-      <c r="D43" s="10" t="n"/>
+      <c r="A43" s="17" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="10" t="n"/>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="10" t="n"/>
-    </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="8" t="inlineStr">
+      <c r="A44" s="17" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="18" t="n"/>
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="n"/>
+      <c r="D45" s="18" t="n"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>💶 CAJA: ARQUEO AL CAMBIO DE TURNO</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t>Tolerancia de descuadre (€):</t>
+        </is>
+      </c>
+      <c r="B47" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="C47" s="22" t="inlineStr">
+        <is>
+          <t>← por debajo de esta cifra el arqueo se da por cuadrado</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="23" t="inlineStr">
+        <is>
+          <t>Caja</t>
+        </is>
+      </c>
+      <c r="B48" s="23" t="inlineStr">
+        <is>
+          <t>Fondo inicial (€)</t>
+        </is>
+      </c>
+      <c r="C48" s="23" t="inlineStr">
+        <is>
+          <t>Efectivo contado (€)</t>
+        </is>
+      </c>
+      <c r="D48" s="23" t="inlineStr">
+        <is>
+          <t>Ventas en efectivo según TPV — lectura Z (€)</t>
+        </is>
+      </c>
+      <c r="E48" s="23" t="inlineStr">
+        <is>
+          <t>Descuadre (€)</t>
+        </is>
+      </c>
+      <c r="F48" s="23" t="inlineStr">
+        <is>
+          <t>Veredicto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="B49" s="21" t="n"/>
+      <c r="C49" s="21" t="n"/>
+      <c r="D49" s="21" t="n"/>
+      <c r="E49" s="25">
+        <f>IF(OR($B49="",$C49="",$D49=""),"",ROUND($C49-$B49-$D49,2))</f>
+        <v/>
+      </c>
+      <c r="F49">
+        <f>IF($E49="","",IF(ABS($E49)&lt;=$B$47,"✓ CUADRA",IF($E49&lt;0,"⛔ FALTAN "&amp;TEXT(-$E49,"0.00")&amp;" €","⚠ SOBRAN "&amp;TEXT($E49,"0.00")&amp;" €")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>Barra</t>
+        </is>
+      </c>
+      <c r="B50" s="21" t="n"/>
+      <c r="C50" s="21" t="n"/>
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="25">
+        <f>IF(OR($B50="",$C50="",$D50=""),"",ROUND($C50-$B50-$D50,2))</f>
+        <v/>
+      </c>
+      <c r="F50">
+        <f>IF($E50="","",IF(ABS($E50)&lt;=$B$47,"✓ CUADRA",IF($E50&lt;0,"⛔ FALTAN "&amp;TEXT(-$E50,"0.00")&amp;" €","⚠ SOBRAN "&amp;TEXT($E50,"0.00")&amp;" €")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="20" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B51" s="26">
+        <f>IF(COUNT(B49:B50)=0,"",ROUND(SUM(B49:B50),2))</f>
+        <v/>
+      </c>
+      <c r="C51" s="26">
+        <f>IF(COUNT(C49:C50)=0,"",ROUND(SUM(C49:C50),2))</f>
+        <v/>
+      </c>
+      <c r="D51" s="26">
+        <f>IF(COUNT(D49:D50)=0,"",ROUND(SUM(D49:D50),2))</f>
+        <v/>
+      </c>
+      <c r="E51" s="26">
+        <f>IF(OR($B51="",$C51="",$D51=""),"",ROUND($C51-$B51-$D51,2))</f>
+        <v/>
+      </c>
+      <c r="F51">
+        <f>IF($E51="","",IF(ABS($E51)&lt;=$B$47,"✓ CUADRA",IF($E51&lt;0,"⛔ FALTAN "&amp;TEXT(-$E51,"0.00")&amp;" €","⚠ SOBRAN "&amp;TEXT($E51,"0.00")&amp;" €")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>Arqueo hecho por: _____________________     ·     Conforme turno entrante: _____________________</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="8" t="n"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="19" t="inlineStr">
+        <is>
+          <t>🌡️ TEMPERATURAS AL CAMBIO DE TURNO (APPCC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="23" t="inlineStr">
+        <is>
+          <t>Equipo</t>
+        </is>
+      </c>
+      <c r="B55" s="23" t="inlineStr">
+        <is>
+          <t>Temperatura (°C)</t>
+        </is>
+      </c>
+      <c r="C55" s="23" t="inlineStr">
+        <is>
+          <t>Mínimo (°C)</t>
+        </is>
+      </c>
+      <c r="D55" s="23" t="inlineStr">
+        <is>
+          <t>Máximo (°C)</t>
+        </is>
+      </c>
+      <c r="E55" s="23" t="inlineStr">
+        <is>
+          <t>Conforme</t>
+        </is>
+      </c>
+      <c r="F55" s="23" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>Cámara de refrigeración</t>
+        </is>
+      </c>
+      <c r="B56" s="27" t="n"/>
+      <c r="C56" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E56">
+        <f>IF(OR($B56="",$C56="",$D56=""),"",IF(AND($B56&gt;=$C56,$B56&lt;=$D56),"✓ CONFORME","⛔ FUERA DE RANGO"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Congelador</t>
+        </is>
+      </c>
+      <c r="B57" s="27" t="n"/>
+      <c r="C57" s="27" t="n">
+        <v>-30</v>
+      </c>
+      <c r="D57" s="27" t="n">
+        <v>-18</v>
+      </c>
+      <c r="E57">
+        <f>IF(OR($B57="",$C57="",$D57=""),"",IF(AND($B57&gt;=$C57,$B57&lt;=$D57),"✓ CONFORME","⛔ FUERA DE RANGO"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="inlineStr">
+        <is>
+          <t>Expositor / vitrina FRÍA</t>
+        </is>
+      </c>
+      <c r="B58" s="27" t="n"/>
+      <c r="C58" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="E58">
+        <f>IF(OR($B58="",$C58="",$D58=""),"",IF(AND($B58&gt;=$C58,$B58&lt;=$D58),"✓ CONFORME","⛔ FUERA DE RANGO"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>Baño maría / mesa caliente</t>
+        </is>
+      </c>
+      <c r="B59" s="27" t="n"/>
+      <c r="C59" s="27" t="n">
+        <v>65</v>
+      </c>
+      <c r="D59" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="E59">
+        <f>IF(OR($B59="",$C59="",$D59=""),"",IF(AND($B59&gt;=$C59,$B59&lt;=$D59),"✓ CONFORME","⛔ FUERA DE RANGO"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="inlineStr">
+        <is>
+          <t>Buffet o vitrina CALIENTE</t>
+        </is>
+      </c>
+      <c r="B60" s="27" t="n"/>
+      <c r="C60" s="27" t="n">
+        <v>65</v>
+      </c>
+      <c r="D60" s="27" t="n">
+        <v>90</v>
+      </c>
+      <c r="E60">
+        <f>IF(OR($B60="",$C60="",$D60=""),"",IF(AND($B60&gt;=$C60,$B60&lt;=$D60),"✓ CONFORME","⛔ FUERA DE RANGO"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="42" customHeight="1">
+      <c r="A61" s="28" t="inlineStr">
+        <is>
+          <t>Quien entrega toma la temperatura DELANTE de quien recibe: es el punto en que el APPCC cambia de responsable. El rango tiene MÍNIMO y máximo: una cámara a −5 °C también es una no conformidad (te ha congelado el producto fresco), y el mantenimiento en caliente sólo es conforme A PARTIR de 65 °C. Fuera de rango, anótalo arriba como incidencia y avisa antes de irte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="8" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="28" t="inlineStr">
         <is>
           <t>OBSERVACIONES GENERALES:</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n"/>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="13" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n"/>
-      <c r="B48" s="12" t="n"/>
-      <c r="C48" s="12" t="n"/>
-      <c r="D48" s="13" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n"/>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="13" t="n"/>
-    </row>
-    <row r="50"/>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="B65" s="29" t="n"/>
+      <c r="C65" s="29" t="n"/>
+      <c r="D65" s="29" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
+      <c r="A66" s="30" t="n"/>
+      <c r="B66" s="31" t="n"/>
+      <c r="C66" s="31" t="n"/>
+      <c r="D66" s="32" t="n"/>
+    </row>
+    <row r="67" ht="30" customHeight="1">
+      <c r="A67" s="30" t="n"/>
+      <c r="B67" s="31" t="n"/>
+      <c r="C67" s="31" t="n"/>
+      <c r="D67" s="32" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="30" t="n"/>
+      <c r="B68" s="31" t="n"/>
+      <c r="C68" s="31" t="n"/>
+      <c r="D68" s="32" t="n"/>
+    </row>
+    <row r="69"/>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>Firma turno saliente: _________________     Firma turno entrante: _________________</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
         <is>
           <t>Hora entrega: ______     Hora recepción: ______</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A51:D51"/>
-    <mergeCell ref="A53:D53"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="18">
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A52:D52"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A52:F52"/>
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="A71:D71"/>
   </mergeCells>
+  <conditionalFormatting sqref="F49:F51">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" stopIfTrue="1" text="FALTAN">
+      <formula>NOT(ISERROR(SEARCH("FALTAN",F49)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="SOBRAN">
+      <formula>NOT(ISERROR(SEARCH("SOBRAN",F49)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" stopIfTrue="1" text="CUADRA">
+      <formula>NOT(ISERROR(SEARCH("CUADRA",F49)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E56:E60">
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="0" stopIfTrue="1" text="FUERA DE RANGO">
+      <formula>NOT(ISERROR(SEARCH("FUERA DE RANGO",E56)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="5" operator="containsText" dxfId="2" stopIfTrue="1" text="CONFORME">
+      <formula>NOT(ISERROR(SEARCH("CONFORME",E56)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="B47" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Tolerancia no válida" error="Escribe un importe entre 0 y 100 €." promptTitle="grupoA-v2 · Tolerancia no válida" prompt="Por debajo de esta cantidad, en más o en menos, el arqueo se da por cuadrado. Cinco euros es lo habitual en un cambio de turno; súbelo o bájalo según tu casa." type="decimal" errorStyle="stop" operator="between">
+      <formula1>0</formula1>
+      <formula2>100</formula2>
+    </dataValidation>
+    <dataValidation sqref="C17:C22" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Gravedad no válida" error="Elige un valor de la lista: las fórmulas de agregación buscan este texto exacto." promptTitle="kitgp-v2 · Gravedad no válida" prompt="TEC-28 · sin lista, cada turno escribe una palabra distinta y el briefing deja de ser comparable de un día para otro." type="list" errorStyle="stop">
+      <formula1>"Alta,Media,Baja"</formula1>
+    </dataValidation>
+    <dataValidation sqref="A25:A30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Prioridad no válida" error="Elige un valor de la lista: las fórmulas de agregación buscan este texto exacto." promptTitle="kitgp-v2 · Prioridad no válida" prompt="Lo que el turno entrante mira primero." type="list" errorStyle="stop">
+      <formula1>"Urgente,Alta,Normal"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
